--- a/NC_sem_outliers.xlsx
+++ b/NC_sem_outliers.xlsx
@@ -431,28 +431,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>3.333333333333333</v>
+        <v>5.8</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>1.75</v>
+        <v>11</v>
+      </c>
+      <c r="K2">
+        <v>10.2</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -508,34 +511,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="E4">
-        <v>6.666666666666667</v>
+        <v>4.2</v>
       </c>
       <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>4.25</v>
-      </c>
-      <c r="H4">
-        <v>0.5</v>
-      </c>
       <c r="I4">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="L4">
-        <v>7.25</v>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M4">
+        <v>6.166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -548,31 +554,34 @@
         </is>
       </c>
       <c r="C5">
-        <v>2.333333333333333</v>
+        <v>8.5</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
+      <c r="H5">
+        <v>12.4</v>
+      </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>7.8</v>
+      </c>
+      <c r="K5">
+        <v>8.5</v>
       </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>9.333333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -671,34 +680,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>3.6</v>
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1.5</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1.333333333333333</v>
-      </c>
       <c r="H8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="L8">
-        <v>2.666666666666667</v>
+        <v>1.8</v>
       </c>
       <c r="M8">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9">
@@ -711,34 +723,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>7.25</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>0.5</v>
+      </c>
+      <c r="E9">
+        <v>1.5</v>
       </c>
       <c r="F9">
-        <v>3.4</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2.5</v>
+      </c>
+      <c r="J9">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="K9">
         <v>3.333333333333333</v>
       </c>
-      <c r="I9">
-        <v>3.4</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
         <v>3</v>
-      </c>
-      <c r="L9">
-        <v>3.6</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -880,31 +895,34 @@
         </is>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>5.8</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>7.2</v>
+      </c>
+      <c r="F13">
+        <v>4.333333333333333</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>7.8</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="L13">
-        <v>7.5</v>
-      </c>
-      <c r="M13">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -960,37 +978,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>6.333333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="E15">
-        <v>9.666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="F15">
-        <v>8.333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="I15">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>5.2</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K15">
-        <v>7.166666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="L15">
-        <v>7.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -1045,6 +1063,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>3.75</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>2.4</v>
+      </c>
+      <c r="F17">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G17">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H17">
+        <v>3.4</v>
+      </c>
+      <c r="I17">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="J17">
+        <v>2.5</v>
+      </c>
+      <c r="K17">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="L17">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M17">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1116,6 +1167,9 @@
       <c r="I19">
         <v>9.199999999999999</v>
       </c>
+      <c r="J19">
+        <v>10.83333333333333</v>
+      </c>
       <c r="K19">
         <v>9.6</v>
       </c>
@@ -1451,6 +1505,9 @@
       <c r="H27">
         <v>7.4</v>
       </c>
+      <c r="I27">
+        <v>6.75</v>
+      </c>
       <c r="J27">
         <v>6</v>
       </c>
@@ -1731,6 +1788,9 @@
       <c r="D34">
         <v>5.333333333333333</v>
       </c>
+      <c r="E34">
+        <v>7.5</v>
+      </c>
       <c r="F34">
         <v>10</v>
       </c>
@@ -1969,34 +2029,28 @@
         </is>
       </c>
       <c r="C40">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>2.8</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>2.166666666666667</v>
+        <v>5.4</v>
       </c>
       <c r="H40">
-        <v>1.6</v>
-      </c>
-      <c r="I40">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="J40">
-        <v>2.333333333333333</v>
+        <v>7.5</v>
       </c>
       <c r="K40">
-        <v>1.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>8.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="M40">
-        <v>3.333333333333333</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="41">
